--- a/inputData/Experiments/inputDataEx5_5_20.xlsx
+++ b/inputData/Experiments/inputDataEx5_5_20.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\Experiments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF8F8592-4AD9-4651-BECF-99E32E83AE50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{288B0339-2D0E-4504-9279-3674E68B769C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="14400" windowHeight="8170" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="PlaneData" sheetId="7" r:id="rId1"/>
@@ -116,7 +116,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -514,12 +514,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94FE46B-0EE8-4D7E-956E-06AD6DDE4FF5}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -527,7 +527,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -535,7 +535,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -543,7 +543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -551,7 +551,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -559,7 +559,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -575,14 +575,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3245F359-CA05-2247-86C6-92433A84B0A2}">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="22.5" customWidth="1"/>
-    <col min="4" max="4" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -596,7 +596,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -613,7 +613,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -630,7 +630,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -647,7 +647,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -664,7 +664,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -681,10 +681,10 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:5">
       <c r="E18" s="4"/>
     </row>
-    <row r="20" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:5">
       <c r="D20" s="4"/>
     </row>
   </sheetData>
@@ -696,13 +696,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0891C305-141D-384C-BB9E-30507F3FCDCC}">
   <dimension ref="A1:X32"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="5" max="5" width="11.875" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" customWidth="1"/>
     <col min="6" max="6" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -722,7 +722,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
@@ -742,7 +742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -762,7 +762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
@@ -776,13 +776,13 @@
         <v>80</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>4</v>
       </c>
@@ -802,7 +802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>5</v>
       </c>
@@ -822,7 +822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>6</v>
       </c>
@@ -836,13 +836,13 @@
         <v>35</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>7</v>
       </c>
@@ -862,7 +862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>8</v>
       </c>
@@ -882,7 +882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>9</v>
       </c>
@@ -902,7 +902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>10</v>
       </c>
@@ -922,7 +922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>11</v>
       </c>
@@ -936,13 +936,13 @@
         <v>20</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>12</v>
       </c>
@@ -962,7 +962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>13</v>
       </c>
@@ -982,7 +982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1002,7 +1002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1022,7 +1022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1042,7 +1042,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1056,13 +1056,13 @@
         <v>100</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1122,7 +1122,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24">
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
@@ -1130,7 +1130,7 @@
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24">
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
@@ -1144,7 +1144,7 @@
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24">
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
@@ -1158,7 +1158,7 @@
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24">
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
@@ -1172,7 +1172,7 @@
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24">
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
@@ -1186,7 +1186,7 @@
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24">
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
@@ -1200,7 +1200,7 @@
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24">
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
@@ -1214,7 +1214,7 @@
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24">
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
@@ -1228,7 +1228,7 @@
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24">
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
@@ -1242,7 +1242,7 @@
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24">
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>

--- a/inputData/Experiments/inputDataEx5_5_20.xlsx
+++ b/inputData/Experiments/inputDataEx5_5_20.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\Experiments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{288B0339-2D0E-4504-9279-3674E68B769C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F7FBA9-25F5-4CFE-855C-3ABE82325546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1520" windowWidth="14400" windowHeight="8170" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="2610" yWindow="1430" windowWidth="14400" windowHeight="8170" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="PlaneData" sheetId="7" r:id="rId1"/>
@@ -776,7 +776,7 @@
         <v>80</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F4">
         <v>0</v>
@@ -836,7 +836,7 @@
         <v>35</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <v>1</v>
@@ -936,7 +936,7 @@
         <v>20</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -1056,7 +1056,7 @@
         <v>100</v>
       </c>
       <c r="E18">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F18">
         <v>0</v>

--- a/inputData/Experiments/inputDataEx5_5_20.xlsx
+++ b/inputData/Experiments/inputDataEx5_5_20.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\Experiments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/Experiments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF8F8592-4AD9-4651-BECF-99E32E83AE50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8383F372-D3E4-934A-996E-F616DA0237B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="13980" yWindow="500" windowWidth="14820" windowHeight="16340" activeTab="3" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="PlaneData" sheetId="7" r:id="rId1"/>
     <sheet name="Infrastructure" sheetId="1" r:id="rId2"/>
     <sheet name="PassengerGroups" sheetId="2" r:id="rId3"/>
+    <sheet name="PassengerGroupsB" sheetId="8" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
   <si>
     <t>type</t>
   </si>
@@ -116,7 +117,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -514,12 +515,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94FE46B-0EE8-4D7E-956E-06AD6DDE4FF5}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -527,7 +528,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -535,7 +536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -543,7 +544,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -551,7 +552,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -559,7 +560,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -575,14 +576,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3245F359-CA05-2247-86C6-92433A84B0A2}">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="22.5" customWidth="1"/>
-    <col min="4" max="4" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -596,7 +597,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -613,7 +614,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -630,7 +631,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -647,7 +648,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -664,7 +665,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -681,10 +682,10 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:5">
       <c r="E18" s="4"/>
     </row>
-    <row r="20" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:5">
       <c r="D20" s="4"/>
     </row>
   </sheetData>
@@ -696,13 +697,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0891C305-141D-384C-BB9E-30507F3FCDCC}">
   <dimension ref="A1:X32"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="5" max="5" width="11.875" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" customWidth="1"/>
     <col min="6" max="6" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -722,7 +723,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>1</v>
       </c>
@@ -742,7 +743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>2</v>
       </c>
@@ -762,7 +763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>3</v>
       </c>
@@ -782,7 +783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>4</v>
       </c>
@@ -802,7 +803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>5</v>
       </c>
@@ -822,7 +823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6">
       <c r="A7">
         <v>6</v>
       </c>
@@ -842,7 +843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6">
       <c r="A8">
         <v>7</v>
       </c>
@@ -862,7 +863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6">
       <c r="A9">
         <v>8</v>
       </c>
@@ -882,7 +883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6">
       <c r="A10">
         <v>9</v>
       </c>
@@ -902,7 +903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6">
       <c r="A11">
         <v>10</v>
       </c>
@@ -922,7 +923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6">
       <c r="A12">
         <v>11</v>
       </c>
@@ -942,7 +943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6">
       <c r="A13">
         <v>12</v>
       </c>
@@ -962,7 +963,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6">
       <c r="A14">
         <v>13</v>
       </c>
@@ -982,7 +983,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1002,7 +1003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1022,7 +1023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1042,7 +1043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1062,7 +1063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1082,7 +1083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1102,7 +1103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1122,7 +1123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24">
       <c r="M23" s="3"/>
       <c r="N23" s="3"/>
       <c r="O23" s="3"/>
@@ -1130,7 +1131,7 @@
       <c r="Q23" s="3"/>
       <c r="R23" s="3"/>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24">
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
       <c r="O24" s="3"/>
@@ -1144,7 +1145,7 @@
       <c r="W24" s="3"/>
       <c r="X24" s="3"/>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24">
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
@@ -1158,7 +1159,7 @@
       <c r="W25" s="3"/>
       <c r="X25" s="3"/>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24">
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
       <c r="O26" s="3"/>
@@ -1172,7 +1173,7 @@
       <c r="W26" s="3"/>
       <c r="X26" s="3"/>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24">
       <c r="M27" s="3"/>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
@@ -1186,7 +1187,7 @@
       <c r="W27" s="3"/>
       <c r="X27" s="3"/>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24">
       <c r="M28" s="3"/>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
@@ -1200,7 +1201,7 @@
       <c r="W28" s="3"/>
       <c r="X28" s="3"/>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24">
       <c r="M29" s="3"/>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
@@ -1214,7 +1215,7 @@
       <c r="W29" s="3"/>
       <c r="X29" s="3"/>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24">
       <c r="M30" s="3"/>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
@@ -1228,7 +1229,7 @@
       <c r="W30" s="3"/>
       <c r="X30" s="3"/>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24">
       <c r="M31" s="3"/>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
@@ -1242,7 +1243,7 @@
       <c r="W31" s="3"/>
       <c r="X31" s="3"/>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24">
       <c r="M32" s="3"/>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
@@ -1259,4 +1260,572 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4259A53C-9B1A-3E4E-AB74-20C813DC4021}">
+  <dimension ref="A1:X32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
+  <cols>
+    <col min="5" max="5" width="11.83203125" customWidth="1"/>
+    <col min="6" max="6" width="11.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>34</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>86</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>19</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>72</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>58</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>91</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8">
+        <v>27</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>4</v>
+      </c>
+      <c r="D9">
+        <v>63</v>
+      </c>
+      <c r="E9">
+        <v>4</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>5</v>
+      </c>
+      <c r="D10">
+        <v>45</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>78</v>
+      </c>
+      <c r="E11">
+        <v>3</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>4</v>
+      </c>
+      <c r="D12">
+        <v>12</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <v>96</v>
+      </c>
+      <c r="E13">
+        <v>4</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>39</v>
+      </c>
+      <c r="E14">
+        <v>3</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+      <c r="C15">
+        <v>4</v>
+      </c>
+      <c r="D15">
+        <v>67</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>4</v>
+      </c>
+      <c r="C16">
+        <v>5</v>
+      </c>
+      <c r="D16">
+        <v>24</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>5</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>83</v>
+      </c>
+      <c r="E17">
+        <v>4</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>3</v>
+      </c>
+      <c r="D18">
+        <v>51</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>3</v>
+      </c>
+      <c r="D19">
+        <v>75</v>
+      </c>
+      <c r="E19">
+        <v>3</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>29</v>
+      </c>
+      <c r="E20">
+        <v>4</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21">
+        <v>88</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24">
+      <c r="M23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="1:24">
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+      <c r="S24" s="3"/>
+      <c r="T24" s="3"/>
+      <c r="U24" s="3"/>
+      <c r="V24" s="3"/>
+      <c r="W24" s="3"/>
+      <c r="X24" s="3"/>
+    </row>
+    <row r="25" spans="1:24">
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="3"/>
+      <c r="T25" s="3"/>
+      <c r="U25" s="3"/>
+      <c r="V25" s="3"/>
+      <c r="W25" s="3"/>
+      <c r="X25" s="3"/>
+    </row>
+    <row r="26" spans="1:24">
+      <c r="M26" s="3"/>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="3"/>
+      <c r="S26" s="3"/>
+      <c r="T26" s="3"/>
+      <c r="U26" s="3"/>
+      <c r="V26" s="3"/>
+      <c r="W26" s="3"/>
+      <c r="X26" s="3"/>
+    </row>
+    <row r="27" spans="1:24">
+      <c r="M27" s="3"/>
+      <c r="N27" s="3"/>
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="3"/>
+      <c r="S27" s="3"/>
+      <c r="T27" s="3"/>
+      <c r="U27" s="3"/>
+      <c r="V27" s="3"/>
+      <c r="W27" s="3"/>
+      <c r="X27" s="3"/>
+    </row>
+    <row r="28" spans="1:24">
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="O28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3"/>
+      <c r="S28" s="3"/>
+      <c r="T28" s="3"/>
+      <c r="U28" s="3"/>
+      <c r="V28" s="3"/>
+      <c r="W28" s="3"/>
+      <c r="X28" s="3"/>
+    </row>
+    <row r="29" spans="1:24">
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+      <c r="O29" s="3"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="3"/>
+      <c r="S29" s="3"/>
+      <c r="T29" s="3"/>
+      <c r="U29" s="3"/>
+      <c r="V29" s="3"/>
+      <c r="W29" s="3"/>
+      <c r="X29" s="3"/>
+    </row>
+    <row r="30" spans="1:24">
+      <c r="M30" s="3"/>
+      <c r="N30" s="3"/>
+      <c r="O30" s="3"/>
+      <c r="P30" s="3"/>
+      <c r="Q30" s="3"/>
+      <c r="R30" s="3"/>
+      <c r="S30" s="3"/>
+      <c r="T30" s="3"/>
+      <c r="U30" s="3"/>
+      <c r="V30" s="3"/>
+      <c r="W30" s="3"/>
+      <c r="X30" s="3"/>
+    </row>
+    <row r="31" spans="1:24">
+      <c r="M31" s="3"/>
+      <c r="N31" s="3"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="3"/>
+      <c r="Q31" s="3"/>
+      <c r="R31" s="3"/>
+      <c r="S31" s="3"/>
+      <c r="T31" s="3"/>
+      <c r="U31" s="3"/>
+      <c r="V31" s="3"/>
+      <c r="W31" s="3"/>
+      <c r="X31" s="3"/>
+    </row>
+    <row r="32" spans="1:24">
+      <c r="M32" s="3"/>
+      <c r="N32" s="3"/>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="3"/>
+      <c r="S32" s="3"/>
+      <c r="T32" s="3"/>
+      <c r="U32" s="3"/>
+      <c r="V32" s="3"/>
+      <c r="W32" s="3"/>
+      <c r="X32" s="3"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/inputData/Experiments/inputDataEx5_5_20.xlsx
+++ b/inputData/Experiments/inputDataEx5_5_20.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kapta\Documents\DTU\Speciale\GitHubFiles\inputData\Experiments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sillewiberg/Desktop/Skole/Speciale/Master-Thesis-eVTOL-1/inputData/Experiments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80F7FBA9-25F5-4CFE-855C-3ABE82325546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B27D4B7-13BA-B34D-B8F6-604A410FEAE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2610" yWindow="1430" windowWidth="14400" windowHeight="8170" activeTab="2" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
+    <workbookView xWindow="2620" yWindow="1440" windowWidth="14400" windowHeight="13600" activeTab="3" xr2:uid="{63F903F0-DEEC-1344-9131-28787FF511C5}"/>
   </bookViews>
   <sheets>
     <sheet name="PlaneData" sheetId="7" r:id="rId1"/>
     <sheet name="Infrastructure" sheetId="1" r:id="rId2"/>
     <sheet name="PassengerGroups" sheetId="2" r:id="rId3"/>
+    <sheet name="PassengerGroupsB" sheetId="8" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
   <si>
     <t>type</t>
   </si>
@@ -514,7 +515,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A94FE46B-0EE8-4D7E-956E-06AD6DDE4FF5}">
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="8.83203125" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -575,7 +576,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3245F359-CA05-2247-86C6-92433A84B0A2}">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="22.5" customWidth="1"/>
     <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
@@ -696,7 +697,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0891C305-141D-384C-BB9E-30507F3FCDCC}">
   <dimension ref="A1:X32"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="5" max="5" width="11.83203125" customWidth="1"/>
     <col min="6" max="6" width="11.5" customWidth="1"/>
@@ -1259,4 +1260,434 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69A4152B-03AF-164B-B238-EA718C660E65}">
+  <dimension ref="A1:F21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>34</v>
+      </c>
+      <c r="E2">
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>86</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <v>19</v>
+      </c>
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>72</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>58</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>91</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8">
+        <v>27</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>4</v>
+      </c>
+      <c r="D9">
+        <v>63</v>
+      </c>
+      <c r="E9">
+        <v>4</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>5</v>
+      </c>
+      <c r="D10">
+        <v>45</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>4</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>78</v>
+      </c>
+      <c r="E11">
+        <v>3</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+      <c r="C12">
+        <v>4</v>
+      </c>
+      <c r="D12">
+        <v>12</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <v>96</v>
+      </c>
+      <c r="E13">
+        <v>4</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>39</v>
+      </c>
+      <c r="E14">
+        <v>3</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>3</v>
+      </c>
+      <c r="C15">
+        <v>4</v>
+      </c>
+      <c r="D15">
+        <v>67</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>4</v>
+      </c>
+      <c r="C16">
+        <v>5</v>
+      </c>
+      <c r="D16">
+        <v>24</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>5</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>83</v>
+      </c>
+      <c r="E17">
+        <v>4</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>3</v>
+      </c>
+      <c r="D18">
+        <v>51</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>3</v>
+      </c>
+      <c r="D19">
+        <v>75</v>
+      </c>
+      <c r="E19">
+        <v>3</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20">
+        <v>29</v>
+      </c>
+      <c r="E20">
+        <v>4</v>
+      </c>
+      <c r="F20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>4</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21">
+        <v>88</v>
+      </c>
+      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>